--- a/journal_de_travail/Excel/journal_de_travail_LDE.xlsx
+++ b/journal_de_travail/Excel/journal_de_travail_LDE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/luc_derre_eduvaud_ch/Documents/ES/Rapport/GENLOG 2/Prog_Pj-Loto/journal_de_travail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LDE Github\Prog_Pj-Loto\journal_de_travail\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="7_{F5BBB245-FAC8-4D4A-ADA2-E86C2F06DB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B293E55-FBD3-4EB4-A94B-F053806D97A5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC70F0E2-23D3-42E9-8957-FBA717A22B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
     <t>Mise à jours GitHub</t>
   </si>
   <si>
-    <t>Mise à jours des structos et de GitHub</t>
+    <t>Mise à jours des structos et de GitHub + création du powerpoint</t>
   </si>
 </sst>
 </file>
@@ -732,7 +732,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="2:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D12" s="9">
         <v>46181</v>
       </c>
